--- a/fedan_rates.xlsx
+++ b/fedan_rates.xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -92,7 +93,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -124,6 +125,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -377,7 +379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="6" min="1" max="1"/>
@@ -635,12 +637,28 @@
           <t>2026-06-10 11:51</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="6" t="n">
         <v>152.08</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>2026-06-10 14:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>46275</v>
+      </c>
+      <c r="I16" t="n">
+        <v>152.14</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:47</t>
         </is>
       </c>
     </row>

--- a/fedan_rates.xlsx
+++ b/fedan_rates.xlsx
@@ -379,7 +379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="6" min="1" max="1"/>
@@ -647,18 +647,34 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>46275</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="6" t="n">
         <v>152.14</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>2026-09-10 14:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C17" t="n">
+        <v>153.19</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-09-28 11:10</t>
         </is>
       </c>
     </row>

--- a/fedan_rates.xlsx
+++ b/fedan_rates.xlsx
@@ -663,18 +663,26 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B17" s="11" t="n">
         <v>46293</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="6" t="n">
         <v>153.19</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>2026-09-28 11:10</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:36</t>
         </is>
       </c>
     </row>

--- a/fedan_rates.xlsx
+++ b/fedan_rates.xlsx
@@ -379,7 +379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="6" min="1" max="1"/>
@@ -677,12 +677,28 @@
           <t>2026-09-28 11:10</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="6" t="n">
         <v>153.2</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>2026-09-28 14:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C18" t="n">
+        <v>153.23</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:53</t>
         </is>
       </c>
     </row>
